--- a/crawler/headpagepb.xlsx
+++ b/crawler/headpagepb.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA261"/>
+  <dimension ref="A1:AA281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -22473,88 +22473,1788 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="A261" s="2" t="inlineStr">
         <is>
           <t>2025/12/30</t>
         </is>
       </c>
-      <c r="B261" t="n">
+      <c r="B261" s="2" t="n">
         <v>2.7</v>
       </c>
-      <c r="C261" t="n">
+      <c r="C261" s="2" t="n">
         <v>5.55</v>
       </c>
-      <c r="D261" t="n">
+      <c r="D261" s="2" t="n">
         <v>2.88</v>
       </c>
-      <c r="E261" t="n">
+      <c r="E261" s="2" t="n">
         <v>3.77</v>
       </c>
-      <c r="F261" t="n">
+      <c r="F261" s="2" t="n">
         <v>6.45</v>
       </c>
-      <c r="G261" t="n">
+      <c r="G261" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="H261" t="n">
+      <c r="H261" s="2" t="n">
         <v>4.8</v>
       </c>
-      <c r="I261" t="n">
+      <c r="I261" s="2" t="n">
         <v>3.77</v>
       </c>
-      <c r="J261" t="n">
+      <c r="J261" s="2" t="n">
         <v>3.68</v>
       </c>
-      <c r="K261" t="n">
+      <c r="K261" s="2" t="n">
         <v>4.14</v>
       </c>
-      <c r="L261" t="n">
+      <c r="L261" s="2" t="n">
         <v>6.16</v>
       </c>
-      <c r="M261" t="n">
+      <c r="M261" s="2" t="n">
         <v>3.29</v>
       </c>
-      <c r="N261" t="n">
+      <c r="N261" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O261" t="n">
+      <c r="O261" s="2" t="n">
         <v>6.17</v>
       </c>
-      <c r="P261" t="n">
+      <c r="P261" s="2" t="n">
         <v>4.68</v>
       </c>
-      <c r="Q261" t="n">
+      <c r="Q261" s="2" t="n">
         <v>1.62</v>
       </c>
-      <c r="R261" t="n">
+      <c r="R261" s="2" t="n">
         <v>2.69</v>
       </c>
-      <c r="S261" t="n">
+      <c r="S261" s="2" t="n">
         <v>1.82</v>
       </c>
-      <c r="T261" t="n">
+      <c r="T261" s="2" t="n">
         <v>7.53</v>
       </c>
-      <c r="U261" t="n">
+      <c r="U261" s="2" t="n">
         <v>3.21</v>
       </c>
-      <c r="V261" t="n">
+      <c r="V261" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="W261" t="n">
+      <c r="W261" s="2" t="n">
         <v>1.55</v>
       </c>
-      <c r="X261" t="n">
+      <c r="X261" s="2" t="n">
         <v>2.38</v>
       </c>
-      <c r="Y261" t="n">
+      <c r="Y261" s="2" t="n">
         <v>6.98</v>
       </c>
-      <c r="Z261" t="n">
+      <c r="Z261" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AA261" t="n">
+      <c r="AA261" s="2" t="n">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="C262" s="2" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="D262" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="G262" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H262" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I262" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="J262" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K262" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="L262" s="2" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="M262" s="2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N262" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O262" s="2" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="P262" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="Q262" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R262" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S262" s="2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T262" s="2" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="U262" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V262" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="W262" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X262" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y262" s="2" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="Z262" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA262" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/05</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C263" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="D263" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="G263" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H263" s="2" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I263" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J263" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="K263" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="L263" s="2" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="M263" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N263" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O263" s="2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P263" s="2" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="Q263" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R263" s="2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="S263" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T263" s="2" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="U263" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V263" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="W263" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X263" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y263" s="2" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="Z263" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA263" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/06</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C264" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D264" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="F264" s="2" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G264" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H264" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I264" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="J264" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="K264" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L264" s="2" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N264" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O264" s="2" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="P264" s="2" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q264" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R264" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="S264" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T264" s="2" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="U264" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="V264" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="W264" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X264" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y264" s="2" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="Z264" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA264" s="2" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/07</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C265" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="D265" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="G265" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="I265" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="J265" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="K265" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="L265" s="2" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N265" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O265" s="2" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="P265" s="2" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="Q265" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R265" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S265" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T265" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U265" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="V265" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="W265" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X265" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y265" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="Z265" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA265" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/08</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C266" s="2" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="G266" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I266" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="J266" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="K266" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L266" s="2" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="M266" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N266" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O266" s="2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="P266" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Q266" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R266" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="S266" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T266" s="2" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="U266" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="V266" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="W266" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X266" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y266" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="Z266" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA266" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/09</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C267" s="2" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="D267" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G267" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H267" s="2" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="I267" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="J267" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="K267" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L267" s="2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N267" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O267" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="P267" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="Q267" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R267" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S267" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T267" s="2" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="U267" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V267" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="W267" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X267" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y267" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="Z267" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA267" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/12</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C268" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="D268" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="G268" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I268" s="2" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="J268" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="K268" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="L268" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="M268" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N268" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O268" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="P268" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q268" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R268" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S268" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T268" s="2" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="U268" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="V268" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="W268" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X268" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y268" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="Z268" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA268" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/13</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C269" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="D269" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="G269" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I269" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="J269" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="K269" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="L269" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="M269" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N269" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O269" s="2" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="P269" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="Q269" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R269" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S269" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T269" s="2" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="U269" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="V269" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="W269" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X269" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y269" s="2" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="Z269" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA269" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/14</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C270" s="2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="D270" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="G270" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="I270" s="2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="J270" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="K270" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L270" s="2" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="M270" s="2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N270" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O270" s="2" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="P270" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Q270" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R270" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S270" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T270" s="2" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="U270" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="V270" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W270" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X270" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y270" s="2" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="Z270" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA270" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/15</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C271" s="2" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="D271" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="G271" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H271" s="2" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="I271" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="J271" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="K271" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="L271" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="M271" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N271" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O271" s="2" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="P271" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q271" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R271" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="S271" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T271" s="2" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="U271" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V271" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W271" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X271" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y271" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="Z271" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA271" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/16</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="G272" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H272" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I272" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="J272" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="K272" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L272" s="2" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="M272" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N272" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O272" s="2" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="P272" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q272" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R272" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="S272" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T272" s="2" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="U272" s="2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V272" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="W272" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X272" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y272" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="Z272" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AA272" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/19</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="D273" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F273" s="2" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G273" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H273" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I273" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="J273" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="K273" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L273" s="2" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="M273" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N273" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O273" s="2" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="P273" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="Q273" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R273" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="S273" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T273" s="2" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="U273" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="V273" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W273" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X273" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y273" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="Z273" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA273" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/20</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C274" s="2" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G274" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H274" s="2" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I274" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="J274" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K274" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="L274" s="2" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="M274" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N274" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O274" s="2" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="P274" s="2" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Q274" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R274" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="S274" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T274" s="2" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="U274" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="V274" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W274" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X274" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y274" s="2" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="Z274" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA274" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/21</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C275" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="D275" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="F275" s="2" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G275" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H275" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="I275" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J275" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="K275" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="L275" s="2" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="M275" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N275" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O275" s="2" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="P275" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="Q275" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R275" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S275" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T275" s="2" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="U275" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V275" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="W275" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X275" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y275" s="2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="Z275" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA275" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/22</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="D276" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="G276" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H276" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I276" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="J276" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="K276" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L276" s="2" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="M276" s="2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N276" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O276" s="2" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="P276" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="Q276" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R276" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S276" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T276" s="2" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="U276" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V276" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="W276" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X276" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y276" s="2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="Z276" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA276" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/23</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C277" s="2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D277" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G277" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H277" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I277" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="J277" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="K277" s="2" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L277" s="2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="M277" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N277" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O277" s="2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="P277" s="2" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Q277" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R277" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="S277" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T277" s="2" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="U277" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V277" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="W277" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X277" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y277" s="2" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="Z277" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AA277" s="2" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/26</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="D278" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F278" s="2" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="G278" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H278" s="2" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I278" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="J278" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K278" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="L278" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M278" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N278" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O278" s="2" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="P278" s="2" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="Q278" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R278" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="S278" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T278" s="2" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="U278" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="V278" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="W278" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X278" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y278" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="Z278" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA278" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/27</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="D279" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="F279" s="2" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="G279" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I279" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="J279" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="K279" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L279" s="2" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M279" s="2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N279" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O279" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="P279" s="2" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="Q279" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R279" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="S279" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T279" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="U279" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V279" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="W279" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X279" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y279" s="2" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="Z279" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA279" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/28</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C280" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="D280" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="G280" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H280" s="2" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I280" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="J280" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="K280" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="L280" s="2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="M280" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N280" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O280" s="2" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="P280" s="2" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="Q280" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R280" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="S280" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T280" s="2" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="U280" s="2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="V280" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="W280" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X280" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y280" s="2" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="Z280" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AA280" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026/1/29</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C281" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="D281" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E281" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F281" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="G281" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H281" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I281" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="J281" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="K281" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="L281" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="M281" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N281" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O281" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="P281" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R281" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S281" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T281" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="U281" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V281" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="W281" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X281" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>

--- a/crawler/headpagepb.xlsx
+++ b/crawler/headpagepb.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA281"/>
+  <dimension ref="A1:AA295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -24173,88 +24173,1278 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
+      <c r="A281" s="2" t="inlineStr">
         <is>
           <t>2026/1/29</t>
         </is>
       </c>
-      <c r="B281" t="n">
+      <c r="B281" s="2" t="n">
         <v>2.85</v>
       </c>
-      <c r="C281" t="n">
+      <c r="C281" s="2" t="n">
         <v>5.69</v>
       </c>
-      <c r="D281" t="n">
+      <c r="D281" s="2" t="n">
         <v>2.88</v>
       </c>
-      <c r="E281" t="n">
+      <c r="E281" s="2" t="n">
         <v>3.69</v>
       </c>
-      <c r="F281" t="n">
+      <c r="F281" s="2" t="n">
         <v>6.51</v>
       </c>
-      <c r="G281" t="n">
+      <c r="G281" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H281" t="n">
+      <c r="H281" s="2" t="n">
         <v>4.83</v>
       </c>
-      <c r="I281" t="n">
+      <c r="I281" s="2" t="n">
         <v>4.07</v>
       </c>
-      <c r="J281" t="n">
+      <c r="J281" s="2" t="n">
         <v>4.02</v>
       </c>
-      <c r="K281" t="n">
+      <c r="K281" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="L281" t="n">
+      <c r="L281" s="2" t="n">
         <v>6.39</v>
       </c>
-      <c r="M281" t="n">
+      <c r="M281" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="N281" t="n">
+      <c r="N281" s="2" t="n">
         <v>2.55</v>
       </c>
-      <c r="O281" t="n">
+      <c r="O281" s="2" t="n">
         <v>6.11</v>
       </c>
-      <c r="P281" t="n">
+      <c r="P281" s="2" t="n">
         <v>4.57</v>
       </c>
-      <c r="Q281" t="n">
+      <c r="Q281" s="2" t="n">
         <v>1.69</v>
       </c>
-      <c r="R281" t="n">
+      <c r="R281" s="2" t="n">
         <v>2.95</v>
       </c>
-      <c r="S281" t="n">
+      <c r="S281" s="2" t="n">
         <v>1.93</v>
       </c>
-      <c r="T281" t="n">
+      <c r="T281" s="2" t="n">
         <v>8.34</v>
       </c>
-      <c r="U281" t="n">
+      <c r="U281" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="V281" t="n">
+      <c r="V281" s="2" t="n">
         <v>3.92</v>
       </c>
-      <c r="W281" t="n">
+      <c r="W281" s="2" t="n">
         <v>1.61</v>
       </c>
-      <c r="X281" t="n">
+      <c r="X281" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="Y281" t="n">
+      <c r="Y281" s="2" t="n">
         <v>7.1</v>
       </c>
-      <c r="Z281" t="n">
+      <c r="Z281" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AA281" t="n">
+      <c r="AA281" s="2" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026/1/30</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C282" s="2" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="D282" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F282" s="2" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G282" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H282" s="2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="I282" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J282" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K282" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L282" s="2" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="M282" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N282" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O282" s="2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="P282" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="Q282" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R282" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S282" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T282" s="2" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="U282" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V282" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="W282" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X282" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y282" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="Z282" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AA282" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/02</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C283" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D283" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G283" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H283" s="2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I283" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="J283" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="K283" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="L283" s="2" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="M283" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N283" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O283" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="P283" s="2" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="Q283" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R283" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="S283" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="T283" s="2" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="U283" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V283" s="2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W283" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X283" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y283" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Z283" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA283" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/03</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C284" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="D284" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G284" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H284" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I284" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="J284" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="K284" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="L284" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="M284" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N284" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O284" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="P284" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q284" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R284" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S284" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T284" s="2" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="U284" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V284" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="W284" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X284" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y284" s="2" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="Z284" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA284" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/04</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C285" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="D285" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F285" s="2" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G285" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H285" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I285" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="J285" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="K285" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="L285" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="M285" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N285" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O285" s="2" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="P285" s="2" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="Q285" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R285" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S285" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T285" s="2" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="U285" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V285" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="W285" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X285" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y285" s="2" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="Z285" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AA285" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/05</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="C286" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="D286" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="G286" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H286" s="2" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="I286" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="J286" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="K286" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L286" s="2" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="M286" s="2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N286" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O286" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="P286" s="2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="Q286" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R286" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S286" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T286" s="2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="U286" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V286" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="W286" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X286" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y286" s="2" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="Z286" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AA286" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/06</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C287" s="2" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="D287" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F287" s="2" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="G287" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H287" s="2" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="I287" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="J287" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="K287" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L287" s="2" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="M287" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N287" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O287" s="2" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="P287" s="2" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="Q287" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R287" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S287" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T287" s="2" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="U287" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V287" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="W287" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X287" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y287" s="2" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="Z287" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AA287" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/09</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C288" s="2" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="D288" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G288" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H288" s="2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I288" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="J288" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="K288" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L288" s="2" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="M288" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N288" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O288" s="2" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="P288" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Q288" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R288" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="S288" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T288" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U288" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V288" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="W288" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X288" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y288" s="2" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="Z288" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AA288" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/10</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C289" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="D289" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F289" s="2" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="G289" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H289" s="2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I289" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="J289" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="K289" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L289" s="2" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M289" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N289" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O289" s="2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="P289" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Q289" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R289" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S289" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T289" s="2" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="U289" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V289" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W289" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X289" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y289" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="Z289" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AA289" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/11</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C290" s="2" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="D290" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="G290" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H290" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I290" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="J290" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="K290" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L290" s="2" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="M290" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N290" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O290" s="2" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="P290" s="2" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="Q290" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R290" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="S290" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T290" s="2" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="U290" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="V290" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="W290" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X290" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y290" s="2" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="Z290" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AA290" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/12</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C291" s="2" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="D291" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G291" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H291" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I291" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="J291" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="K291" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="L291" s="2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M291" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N291" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O291" s="2" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="P291" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Q291" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R291" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S291" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T291" s="2" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="U291" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="V291" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="W291" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X291" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y291" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="Z291" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AA291" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/13</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C292" s="2" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="D292" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F292" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G292" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H292" s="2" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="I292" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="J292" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K292" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="L292" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="M292" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N292" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O292" s="2" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="P292" s="2" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="Q292" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R292" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="S292" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T292" s="2" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="U292" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V292" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W292" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X292" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y292" s="2" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="Z292" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AA292" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/24</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C293" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="D293" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G293" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H293" s="2" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I293" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J293" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="K293" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L293" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="M293" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N293" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O293" s="2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="P293" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="Q293" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R293" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="S293" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T293" s="2" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="U293" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V293" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="W293" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X293" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y293" s="2" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="Z293" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AA293" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/25</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C294" s="2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D294" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="G294" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H294" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="I294" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="J294" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="K294" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L294" s="2" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="M294" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N294" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O294" s="2" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="P294" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="Q294" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R294" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="S294" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T294" s="2" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="U294" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V294" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="W294" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X294" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y294" s="2" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="Z294" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AA294" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026/2/26</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C295" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="D295" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E295" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="F295" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H295" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I295" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="J295" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="K295" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="L295" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="M295" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N295" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O295" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="P295" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R295" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="S295" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T295" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="U295" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V295" t="n">
+        <v>4</v>
+      </c>
+      <c r="W295" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X295" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>

--- a/crawler/headpagepb.xlsx
+++ b/crawler/headpagepb.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA295"/>
+  <dimension ref="A1:AA317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -25363,88 +25363,1958 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
+      <c r="A295" s="2" t="inlineStr">
         <is>
           <t>2026/2/26</t>
         </is>
       </c>
-      <c r="B295" t="n">
+      <c r="B295" s="2" t="n">
         <v>2.89</v>
       </c>
-      <c r="C295" t="n">
+      <c r="C295" s="2" t="n">
         <v>5.77</v>
       </c>
-      <c r="D295" t="n">
+      <c r="D295" s="2" t="n">
         <v>2.92</v>
       </c>
-      <c r="E295" t="n">
+      <c r="E295" s="2" t="n">
         <v>3.68</v>
       </c>
-      <c r="F295" t="n">
+      <c r="F295" s="2" t="n">
         <v>6.64</v>
       </c>
-      <c r="G295" t="n">
+      <c r="G295" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H295" t="n">
+      <c r="H295" s="2" t="n">
         <v>4.89</v>
       </c>
-      <c r="I295" t="n">
+      <c r="I295" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="J295" t="n">
+      <c r="J295" s="2" t="n">
         <v>4.16</v>
       </c>
-      <c r="K295" t="n">
+      <c r="K295" s="2" t="n">
         <v>4.17</v>
       </c>
-      <c r="L295" t="n">
+      <c r="L295" s="2" t="n">
         <v>6.54</v>
       </c>
-      <c r="M295" t="n">
+      <c r="M295" s="2" t="n">
         <v>3.27</v>
       </c>
-      <c r="N295" t="n">
+      <c r="N295" s="2" t="n">
         <v>2.49</v>
       </c>
-      <c r="O295" t="n">
+      <c r="O295" s="2" t="n">
         <v>6.26</v>
       </c>
-      <c r="P295" t="n">
+      <c r="P295" s="2" t="n">
         <v>4.69</v>
       </c>
-      <c r="Q295" t="n">
+      <c r="Q295" s="2" t="n">
         <v>1.68</v>
       </c>
-      <c r="R295" t="n">
+      <c r="R295" s="2" t="n">
         <v>3.03</v>
       </c>
-      <c r="S295" t="n">
+      <c r="S295" s="2" t="n">
         <v>1.95</v>
       </c>
-      <c r="T295" t="n">
+      <c r="T295" s="2" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="U295" t="n">
+      <c r="U295" s="2" t="n">
         <v>3.22</v>
       </c>
-      <c r="V295" t="n">
+      <c r="V295" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="W295" t="n">
+      <c r="W295" s="2" t="n">
         <v>1.6</v>
       </c>
-      <c r="X295" t="n">
+      <c r="X295" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="Y295" t="n">
+      <c r="Y295" s="2" t="n">
         <v>6.35</v>
       </c>
-      <c r="Z295" t="n">
+      <c r="Z295" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AA295" t="n">
+      <c r="AA295" s="2" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026/2/27</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C296" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="D296" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F296" s="2" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="G296" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H296" s="2" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="I296" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="J296" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="K296" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L296" s="2" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="M296" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N296" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O296" s="2" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="P296" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Q296" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R296" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="S296" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T296" s="2" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="U296" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V296" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="W296" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X296" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y296" s="2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="Z296" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AA296" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/02</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C297" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="D297" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="G297" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H297" s="2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I297" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="J297" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K297" s="2" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L297" s="2" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="M297" s="2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N297" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O297" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="P297" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q297" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R297" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="S297" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T297" s="2" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="U297" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V297" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W297" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X297" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y297" s="2" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="Z297" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AA297" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/03</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C298" s="2" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="D298" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="G298" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H298" s="2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I298" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="J298" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K298" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L298" s="2" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="M298" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N298" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O298" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="P298" s="2" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="Q298" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R298" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S298" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T298" s="2" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="U298" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="V298" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W298" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X298" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y298" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="Z298" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AA298" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/04</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C299" s="2" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D299" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="F299" s="2" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G299" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H299" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="I299" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="J299" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="K299" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L299" s="2" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="M299" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N299" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O299" s="2" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="P299" s="2" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="Q299" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R299" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="S299" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T299" s="2" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="U299" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V299" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="W299" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X299" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y299" s="2" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="Z299" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA299" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/05</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C300" s="2" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="D300" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="G300" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H300" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I300" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="J300" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K300" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="L300" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="M300" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N300" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O300" s="2" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="P300" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q300" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R300" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S300" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T300" s="2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="U300" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V300" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="W300" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X300" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y300" s="2" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="Z300" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA300" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/06</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C301" s="2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="D301" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="G301" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H301" s="2" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="I301" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="J301" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="K301" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L301" s="2" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="M301" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N301" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O301" s="2" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="P301" s="2" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Q301" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R301" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S301" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T301" s="2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="U301" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="V301" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="W301" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X301" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y301" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="Z301" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AA301" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/09</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C302" s="2" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="D302" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="G302" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H302" s="2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I302" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="J302" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K302" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L302" s="2" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="M302" s="2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N302" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O302" s="2" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="P302" s="2" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="Q302" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R302" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S302" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T302" s="2" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="U302" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V302" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W302" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X302" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y302" s="2" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="Z302" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA302" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/10</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C303" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="D303" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="G303" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H303" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I303" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="J303" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K303" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L303" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N303" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O303" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="P303" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Q303" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R303" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="S303" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T303" s="2" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="U303" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V303" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="W303" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X303" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y303" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Z303" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AA303" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/11</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C304" s="2" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="D304" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="G304" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H304" s="2" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I304" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="J304" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="K304" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L304" s="2" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="M304" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N304" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O304" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P304" s="2" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q304" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R304" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="S304" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T304" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="U304" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V304" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="W304" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X304" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y304" s="2" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="Z304" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA304" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/12</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C305" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="D305" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G305" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H305" s="2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="I305" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="J305" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="K305" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L305" s="2" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N305" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O305" s="2" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="P305" s="2" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="Q305" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R305" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S305" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T305" s="2" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="U305" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V305" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="W305" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X305" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y305" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z305" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA305" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/13</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C306" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="D306" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F306" s="2" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="G306" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H306" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I306" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="J306" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="K306" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="L306" s="2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M306" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N306" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O306" s="2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="P306" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q306" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R306" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S306" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T306" s="2" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="U306" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V306" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="W306" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X306" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y306" s="2" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="Z306" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA306" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/16</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C307" s="2" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="D307" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="G307" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H307" s="2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I307" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J307" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K307" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L307" s="2" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="M307" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="N307" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O307" s="2" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="P307" s="2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="Q307" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R307" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S307" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T307" s="2" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="U307" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="V307" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="W307" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X307" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y307" s="2" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="Z307" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AA307" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/17</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C308" s="2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="D308" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="G308" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H308" s="2" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="I308" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J308" s="2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="K308" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L308" s="2" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="M308" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N308" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O308" s="2" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="P308" s="2" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="Q308" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R308" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S308" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T308" s="2" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="U308" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V308" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W308" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X308" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y308" s="2" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="Z308" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA308" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/18</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C309" s="2" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="D309" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E309" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="F309" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G309" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H309" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I309" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="J309" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K309" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L309" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="M309" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N309" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O309" s="2" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="P309" s="2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="Q309" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R309" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S309" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T309" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="U309" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="V309" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="W309" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X309" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y309" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="Z309" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA309" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/19</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C310" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D310" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F310" s="2" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="G310" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H310" s="2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="I310" s="2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="J310" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K310" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L310" s="2" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="M310" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N310" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O310" s="2" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="P310" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q310" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R310" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="S310" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="T310" s="2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="U310" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V310" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="W310" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X310" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y310" s="2" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="Z310" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA310" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/20</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C311" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D311" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E311" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F311" s="2" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="G311" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H311" s="2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="I311" s="2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="J311" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K311" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L311" s="2" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N311" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O311" s="2" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="P311" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q311" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R311" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S311" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T311" s="2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="U311" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V311" s="2" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="W311" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X311" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y311" s="2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="Z311" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AA311" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/23</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C312" s="2" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="D312" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="F312" s="2" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G312" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H312" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I312" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J312" s="2" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="K312" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="L312" s="2" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="M312" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N312" s="2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O312" s="2" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P312" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="Q312" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R312" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S312" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T312" s="2" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="U312" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V312" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="W312" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X312" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y312" s="2" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="Z312" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA312" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/24</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="C313" s="2" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D313" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="F313" s="2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G313" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H313" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="I313" s="2" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="J313" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K313" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="L313" s="2" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="M313" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N313" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O313" s="2" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="P313" s="2" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="Q313" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R313" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S313" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T313" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="U313" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V313" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="W313" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X313" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y313" s="2" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="Z313" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA313" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/25</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C314" s="2" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="D314" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E314" s="2" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="F314" s="2" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="G314" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H314" s="2" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="I314" s="2" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="J314" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="K314" s="2" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L314" s="2" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="M314" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N314" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O314" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P314" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Q314" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R314" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S314" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T314" s="2" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="U314" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V314" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W314" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X314" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Y314" s="2" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="Z314" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA314" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/26</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C315" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D315" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E315" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="F315" s="2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="G315" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H315" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="I315" s="2" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="J315" s="2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="K315" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L315" s="2" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="M315" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N315" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O315" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="P315" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q315" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R315" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S315" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T315" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="U315" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V315" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="W315" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X315" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y315" s="2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z315" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA315" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/27</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C316" s="2" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="D316" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E316" s="2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="G316" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H316" s="2" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I316" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J316" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K316" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="L316" s="2" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="M316" s="2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N316" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O316" s="2" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="P316" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Q316" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R316" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S316" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T316" s="2" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="U316" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V316" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="W316" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X316" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y316" s="2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="Z316" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA316" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026/3/30</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C317" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="D317" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E317" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="F317" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="G317" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H317" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I317" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J317" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K317" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="L317" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="M317" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N317" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O317" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="P317" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R317" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S317" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T317" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="U317" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V317" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W317" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X317" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>

--- a/crawler/headpagepb.xlsx
+++ b/crawler/headpagepb.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA317"/>
+  <dimension ref="A1:AA337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -27233,88 +27233,1788 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
+      <c r="A317" s="2" t="inlineStr">
         <is>
           <t>2026/3/30</t>
         </is>
       </c>
-      <c r="B317" t="n">
+      <c r="B317" s="2" t="n">
         <v>2.73</v>
       </c>
-      <c r="C317" t="n">
+      <c r="C317" s="2" t="n">
         <v>5.55</v>
       </c>
-      <c r="D317" t="n">
+      <c r="D317" s="2" t="n">
         <v>2.83</v>
       </c>
-      <c r="E317" t="n">
+      <c r="E317" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="F317" t="n">
+      <c r="F317" s="2" t="n">
         <v>6.39</v>
       </c>
-      <c r="G317" t="n">
+      <c r="G317" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="H317" t="n">
+      <c r="H317" s="2" t="n">
         <v>4.71</v>
       </c>
-      <c r="I317" t="n">
+      <c r="I317" s="2" t="n">
         <v>3.72</v>
       </c>
-      <c r="J317" t="n">
+      <c r="J317" s="2" t="n">
         <v>3.69</v>
       </c>
-      <c r="K317" t="n">
+      <c r="K317" s="2" t="n">
         <v>4.12</v>
       </c>
-      <c r="L317" t="n">
+      <c r="L317" s="2" t="n">
         <v>6.05</v>
       </c>
-      <c r="M317" t="n">
+      <c r="M317" s="2" t="n">
         <v>3.41</v>
       </c>
-      <c r="N317" t="n">
+      <c r="N317" s="2" t="n">
         <v>2.32</v>
       </c>
-      <c r="O317" t="n">
+      <c r="O317" s="2" t="n">
         <v>6.58</v>
       </c>
-      <c r="P317" t="n">
+      <c r="P317" s="2" t="n">
         <v>4.65</v>
       </c>
-      <c r="Q317" t="n">
+      <c r="Q317" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="R317" t="n">
+      <c r="R317" s="2" t="n">
         <v>2.76</v>
       </c>
-      <c r="S317" t="n">
+      <c r="S317" s="2" t="n">
         <v>1.82</v>
       </c>
-      <c r="T317" t="n">
+      <c r="T317" s="2" t="n">
         <v>7.03</v>
       </c>
-      <c r="U317" t="n">
+      <c r="U317" s="2" t="n">
         <v>3.08</v>
       </c>
-      <c r="V317" t="n">
+      <c r="V317" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="W317" t="n">
+      <c r="W317" s="2" t="n">
         <v>1.52</v>
       </c>
-      <c r="X317" t="n">
+      <c r="X317" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y317" t="n">
+      <c r="Y317" s="2" t="n">
         <v>5.76</v>
       </c>
-      <c r="Z317" t="n">
+      <c r="Z317" s="2" t="n">
         <v>1.06</v>
       </c>
-      <c r="AA317" t="n">
+      <c r="AA317" s="2" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2026/3/31</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C318" s="2" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="D318" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E318" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G318" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H318" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="I318" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="J318" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="K318" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L318" s="2" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="M318" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N318" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O318" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="P318" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q318" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R318" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="S318" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T318" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="U318" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V318" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="W318" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X318" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y318" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="Z318" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA318" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/01</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C319" s="2" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="D319" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E319" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G319" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H319" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="I319" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="J319" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="K319" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L319" s="2" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="M319" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N319" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O319" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="P319" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q319" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R319" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="S319" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T319" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="U319" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V319" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="W319" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X319" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y319" s="2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="Z319" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA319" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/02</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="C320" s="2" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="D320" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E320" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="F320" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="G320" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H320" s="2" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I320" s="2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J320" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="K320" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="L320" s="2" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="M320" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N320" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O320" s="2" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="P320" s="2" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q320" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R320" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S320" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T320" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="U320" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V320" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="W320" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X320" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y320" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="Z320" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA320" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/03</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C321" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D321" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E321" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G321" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H321" s="2" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="I321" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J321" s="2" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="K321" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L321" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M321" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N321" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O321" s="2" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="P321" s="2" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q321" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R321" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="S321" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T321" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="U321" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V321" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="W321" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X321" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y321" s="2" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="Z321" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA321" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/07</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C322" s="2" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="D322" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E322" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="F322" s="2" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="G322" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H322" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="I322" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="J322" s="2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="K322" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="L322" s="2" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M322" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N322" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O322" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P322" s="2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q322" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R322" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="S322" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T322" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="U322" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V322" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="W322" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X322" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y322" s="2" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Z322" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA322" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/08</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C323" s="2" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="D323" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E323" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="F323" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G323" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H323" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="I323" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="J323" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K323" s="2" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L323" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="M323" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N323" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O323" s="2" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="P323" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q323" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R323" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="S323" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T323" s="2" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="U323" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V323" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="W323" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X323" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y323" s="2" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="Z323" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA323" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/09</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C324" s="2" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="D324" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E324" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F324" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="G324" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H324" s="2" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="I324" s="2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="J324" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="K324" s="2" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L324" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="M324" s="2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N324" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O324" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="P324" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Q324" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R324" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="S324" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T324" s="2" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="U324" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V324" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W324" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X324" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y324" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="Z324" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA324" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/10</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C325" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="D325" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E325" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="G325" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H325" s="2" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="I325" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="J325" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K325" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="L325" s="2" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="M325" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N325" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O325" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P325" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="Q325" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R325" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="S325" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T325" s="2" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="U325" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="V325" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W325" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X325" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y325" s="2" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="Z325" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA325" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/13</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C326" s="2" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="D326" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E326" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="F326" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G326" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I326" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="J326" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K326" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="L326" s="2" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="M326" s="2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N326" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O326" s="2" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="P326" s="2" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="Q326" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R326" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S326" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="T326" s="2" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="U326" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="V326" s="2" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="W326" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X326" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y326" s="2" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="Z326" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA326" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/14</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C327" s="2" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="D327" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E327" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="F327" s="2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="G327" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H327" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I327" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="J327" s="2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="K327" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="L327" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M327" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N327" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O327" s="2" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="P327" s="2" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q327" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R327" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="S327" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T327" s="2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="U327" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V327" s="2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="W327" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X327" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y327" s="2" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="Z327" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA327" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/15</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C328" s="2" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="D328" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E328" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="F328" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="G328" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H328" s="2" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="I328" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="J328" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K328" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L328" s="2" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="M328" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N328" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O328" s="2" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="P328" s="2" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="Q328" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R328" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S328" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T328" s="2" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="U328" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V328" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="W328" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X328" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y328" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="Z328" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA328" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/16</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C329" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="D329" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E329" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F329" s="2" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G329" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H329" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="I329" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J329" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="K329" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L329" s="2" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="M329" s="2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="N329" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O329" s="2" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="P329" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="Q329" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R329" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S329" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T329" s="2" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="U329" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V329" s="2" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="W329" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X329" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y329" s="2" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="Z329" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA329" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/17</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C330" s="2" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="D330" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E330" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F330" s="2" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="G330" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H330" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="I330" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="J330" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="K330" s="2" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="L330" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M330" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="N330" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O330" s="2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="P330" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q330" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R330" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="S330" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T330" s="2" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="U330" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V330" s="2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="W330" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X330" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y330" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="Z330" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AA330" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/20</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C331" s="2" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="D331" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E331" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F331" s="2" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="G331" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H331" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I331" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="J331" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="K331" s="2" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="L331" s="2" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="M331" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="N331" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O331" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="P331" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q331" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R331" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S331" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T331" s="2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="U331" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="V331" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="W331" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X331" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y331" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Z331" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AA331" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/21</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C332" s="2" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="D332" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E332" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="G332" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H332" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="I332" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="J332" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="K332" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L332" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M332" s="2" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N332" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O332" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="P332" s="2" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="Q332" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R332" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S332" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T332" s="2" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="U332" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V332" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="W332" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X332" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y332" s="2" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="Z332" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA332" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/22</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="C333" s="2" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="D333" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="G333" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H333" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I333" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="J333" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="K333" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="L333" s="2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="M333" s="2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N333" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O333" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="P333" s="2" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="Q333" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R333" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="S333" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T333" s="2" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="U333" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="V333" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W333" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X333" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y333" s="2" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="Z333" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA333" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C334" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="D334" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E334" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="F334" s="2" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="G334" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H334" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I334" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="J334" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="K334" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L334" s="2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="M334" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N334" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O334" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="P334" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="Q334" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R334" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S334" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T334" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="U334" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="V334" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="W334" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X334" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y334" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="Z334" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA334" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/27</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C335" s="2" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="D335" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="F335" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="G335" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H335" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I335" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="J335" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="K335" s="2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="L335" s="2" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="M335" s="2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N335" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O335" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="P335" s="2" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q335" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R335" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S335" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T335" s="2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="U335" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="V335" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W335" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X335" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y335" s="2" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="Z335" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA335" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/28</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C336" s="2" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="D336" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E336" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="F336" s="2" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="G336" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H336" s="2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I336" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J336" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="K336" s="2" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="L336" s="2" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="M336" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N336" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O336" s="2" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="P336" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="Q336" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R336" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="S336" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T336" s="2" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="U336" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V336" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="W336" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X336" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y336" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="Z336" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA336" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026/4/29</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C337" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="D337" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E337" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F337" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="G337" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H337" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="I337" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="J337" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="K337" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="L337" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M337" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N337" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O337" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="P337" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R337" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="S337" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T337" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="U337" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V337" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="W337" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X337" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA337" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>

--- a/crawler/headpagepb.xlsx
+++ b/crawler/headpagepb.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA337"/>
+  <dimension ref="A1:AA355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -28933,88 +28933,1618 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
+      <c r="A337" s="2" t="inlineStr">
         <is>
           <t>2026/4/29</t>
         </is>
       </c>
-      <c r="B337" t="n">
+      <c r="B337" s="2" t="n">
         <v>2.9</v>
       </c>
-      <c r="C337" t="n">
+      <c r="C337" s="2" t="n">
         <v>5.86</v>
       </c>
-      <c r="D337" t="n">
+      <c r="D337" s="2" t="n">
         <v>3.02</v>
       </c>
-      <c r="E337" t="n">
+      <c r="E337" s="2" t="n">
         <v>3.93</v>
       </c>
-      <c r="F337" t="n">
+      <c r="F337" s="2" t="n">
         <v>6.82</v>
       </c>
-      <c r="G337" t="n">
+      <c r="G337" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="H337" t="n">
+      <c r="H337" s="2" t="n">
         <v>4.92</v>
       </c>
-      <c r="I337" t="n">
+      <c r="I337" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="J337" t="n">
+      <c r="J337" s="2" t="n">
         <v>3.98</v>
       </c>
-      <c r="K337" t="n">
+      <c r="K337" s="2" t="n">
         <v>4.46</v>
       </c>
-      <c r="L337" t="n">
+      <c r="L337" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="M337" t="n">
+      <c r="M337" s="2" t="n">
         <v>3.42</v>
       </c>
-      <c r="N337" t="n">
+      <c r="N337" s="2" t="n">
         <v>2.33</v>
       </c>
-      <c r="O337" t="n">
+      <c r="O337" s="2" t="n">
         <v>6.92</v>
       </c>
-      <c r="P337" t="n">
+      <c r="P337" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="Q337" t="n">
+      <c r="Q337" s="2" t="n">
         <v>1.66</v>
       </c>
-      <c r="R337" t="n">
+      <c r="R337" s="2" t="n">
         <v>2.91</v>
       </c>
-      <c r="S337" t="n">
+      <c r="S337" s="2" t="n">
         <v>1.91</v>
       </c>
-      <c r="T337" t="n">
+      <c r="T337" s="2" t="n">
         <v>7.95</v>
       </c>
-      <c r="U337" t="n">
+      <c r="U337" s="2" t="n">
         <v>3.24</v>
       </c>
-      <c r="V337" t="n">
+      <c r="V337" s="2" t="n">
         <v>4.36</v>
       </c>
-      <c r="W337" t="n">
+      <c r="W337" s="2" t="n">
         <v>1.58</v>
       </c>
-      <c r="X337" t="n">
+      <c r="X337" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="Y337" t="n">
+      <c r="Y337" s="2" t="n">
         <v>6.59</v>
       </c>
-      <c r="Z337" t="n">
+      <c r="Z337" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AA337" t="n">
+      <c r="AA337" s="2" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2026/4/30</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C338" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="D338" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E338" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F338" s="2" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="G338" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H338" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="I338" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="J338" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="K338" s="2" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="L338" s="2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="M338" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N338" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O338" s="2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="P338" s="2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q338" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R338" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S338" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T338" s="2" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="U338" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V338" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="W338" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X338" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y338" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="Z338" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AA338" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/06</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="C339" s="2" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="D339" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E339" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F339" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="G339" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H339" s="2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I339" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="J339" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="K339" s="2" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="L339" s="2" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="M339" s="2" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N339" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O339" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P339" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Q339" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R339" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="S339" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T339" s="2" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="U339" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="V339" s="2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="W339" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X339" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y339" s="2" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="Z339" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AA339" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/07</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="C340" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D340" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E340" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="G340" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H340" s="2" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="I340" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J340" s="2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="K340" s="2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="L340" s="2" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="M340" s="2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N340" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O340" s="2" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="P340" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="Q340" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R340" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S340" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T340" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="U340" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V340" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W340" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X340" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y340" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="Z340" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AA340" s="2" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/08</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="C341" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="D341" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E341" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F341" s="2" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="G341" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H341" s="2" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="I341" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J341" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K341" s="2" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="L341" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="M341" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N341" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O341" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="P341" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="Q341" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R341" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="S341" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T341" s="2" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="U341" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="V341" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="W341" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X341" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y341" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Z341" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA341" s="2" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C342" s="2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D342" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E342" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F342" s="2" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="G342" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H342" s="2" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="I342" s="2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="J342" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="K342" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="L342" s="2" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="M342" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="N342" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O342" s="2" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="P342" s="2" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="Q342" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R342" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="S342" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T342" s="2" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="U342" s="2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="V342" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W342" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X342" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y342" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="Z342" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AA342" s="2" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/12</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="C343" s="2" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="D343" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E343" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F343" s="2" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="G343" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H343" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I343" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="J343" s="2" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="K343" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="L343" s="2" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="M343" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N343" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O343" s="2" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="P343" s="2" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="Q343" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R343" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S343" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T343" s="2" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="U343" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V343" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="W343" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X343" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y343" s="2" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="Z343" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AA343" s="2" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/13</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="C344" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D344" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E344" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F344" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="G344" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H344" s="2" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="I344" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J344" s="2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="K344" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L344" s="2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="M344" s="2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N344" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O344" s="2" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="P344" s="2" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="Q344" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R344" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S344" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T344" s="2" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="U344" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="V344" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="W344" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X344" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y344" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="Z344" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AA344" s="2" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/14</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C345" s="2" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="D345" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E345" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F345" s="2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="G345" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H345" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I345" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="J345" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K345" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="L345" s="2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="M345" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N345" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O345" s="2" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="P345" s="2" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="Q345" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R345" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="S345" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T345" s="2" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="U345" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="V345" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W345" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X345" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y345" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z345" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AA345" s="2" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/15</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C346" s="2" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="D346" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E346" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F346" s="2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="G346" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H346" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I346" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="J346" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K346" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="L346" s="2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="M346" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N346" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O346" s="2" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="P346" s="2" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="Q346" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R346" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="S346" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T346" s="2" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="U346" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V346" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="W346" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X346" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y346" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="Z346" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AA346" s="2" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/18</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="C347" s="2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="D347" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E347" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F347" s="2" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="G347" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H347" s="2" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I347" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J347" s="2" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="K347" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="L347" s="2" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="M347" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N347" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O347" s="2" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="P347" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q347" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R347" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="S347" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T347" s="2" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="U347" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="V347" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="W347" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X347" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y347" s="2" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="Z347" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AA347" s="2" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/19</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="C348" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D348" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E348" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F348" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="G348" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H348" s="2" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="I348" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J348" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K348" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="L348" s="2" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="M348" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N348" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O348" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="P348" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="Q348" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R348" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="S348" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T348" s="2" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="U348" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="V348" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="W348" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X348" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y348" s="2" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="Z348" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AA348" s="2" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/20</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="C349" s="2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="D349" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E349" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F349" s="2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="G349" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H349" s="2" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="I349" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="J349" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="K349" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="L349" s="2" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="M349" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N349" s="2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O349" s="2" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="P349" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Q349" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R349" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S349" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T349" s="2" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="U349" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V349" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="W349" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X349" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y349" s="2" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="Z349" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AA349" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/21</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C350" s="2" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="D350" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E350" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F350" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="G350" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H350" s="2" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="I350" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="J350" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="K350" s="2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="L350" s="2" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="M350" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N350" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O350" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="P350" s="2" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="Q350" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R350" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S350" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T350" s="2" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="U350" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V350" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="W350" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X350" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y350" s="2" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="Z350" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AA350" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/22</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="C351" s="2" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="D351" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E351" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F351" s="2" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="G351" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H351" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I351" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="J351" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K351" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="L351" s="2" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="M351" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N351" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O351" s="2" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="P351" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="Q351" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R351" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="S351" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T351" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="U351" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V351" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="W351" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X351" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y351" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="Z351" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA351" s="2" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/25</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="C352" s="2" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="D352" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E352" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F352" s="2" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="G352" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H352" s="2" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="I352" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="J352" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="K352" s="2" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="L352" s="2" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="M352" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N352" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O352" s="2" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="P352" s="2" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="Q352" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R352" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="S352" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T352" s="2" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="U352" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V352" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="W352" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X352" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y352" s="2" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="Z352" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA352" s="2" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/26</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="C353" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="D353" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E353" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F353" s="2" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="G353" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H353" s="2" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="I353" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="J353" s="2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="K353" s="2" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="L353" s="2" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="M353" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N353" s="2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O353" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="P353" s="2" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="Q353" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R353" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S353" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T353" s="2" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="U353" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="V353" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="W353" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X353" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y353" s="2" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="Z353" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA353" s="2" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/27</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="C354" s="2" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="D354" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E354" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F354" s="2" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="G354" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H354" s="2" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="I354" s="2" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="J354" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="K354" s="2" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="L354" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M354" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N354" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O354" s="2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="P354" s="2" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="Q354" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R354" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S354" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T354" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="U354" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V354" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="W354" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X354" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y354" s="2" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="Z354" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA354" s="2" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026/5/28</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>3</v>
+      </c>
+      <c r="C355" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="D355" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="E355" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="F355" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="G355" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H355" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="I355" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="J355" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="K355" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="L355" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="M355" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N355" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O355" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P355" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R355" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="S355" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T355" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="U355" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V355" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W355" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X355" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/crawler/headpagepb.xlsx
+++ b/crawler/headpagepb.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA355"/>
+  <dimension ref="A1:AA376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -30463,88 +30463,1873 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
+      <c r="A355" s="2" t="inlineStr">
         <is>
           <t>2026/5/28</t>
         </is>
       </c>
-      <c r="B355" t="n">
+      <c r="B355" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C355" t="n">
+      <c r="C355" s="2" t="n">
         <v>6.47</v>
       </c>
-      <c r="D355" t="n">
+      <c r="D355" s="2" t="n">
         <v>3.14</v>
       </c>
-      <c r="E355" t="n">
+      <c r="E355" s="2" t="n">
         <v>4.11</v>
       </c>
-      <c r="F355" t="n">
+      <c r="F355" s="2" t="n">
         <v>7.67</v>
       </c>
-      <c r="G355" t="n">
+      <c r="G355" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="H355" t="n">
+      <c r="H355" s="2" t="n">
         <v>5.34</v>
       </c>
-      <c r="I355" t="n">
+      <c r="I355" s="2" t="n">
         <v>4.32</v>
       </c>
-      <c r="J355" t="n">
+      <c r="J355" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="K355" t="n">
+      <c r="K355" s="2" t="n">
         <v>4.87</v>
       </c>
-      <c r="L355" t="n">
+      <c r="L355" s="2" t="n">
         <v>8.17</v>
       </c>
-      <c r="M355" t="n">
+      <c r="M355" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="N355" t="n">
+      <c r="N355" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="O355" t="n">
+      <c r="O355" s="2" t="n">
         <v>7.8</v>
       </c>
-      <c r="P355" t="n">
+      <c r="P355" s="2" t="n">
         <v>5.19</v>
       </c>
-      <c r="Q355" t="n">
+      <c r="Q355" s="2" t="n">
         <v>1.65</v>
       </c>
-      <c r="R355" t="n">
+      <c r="R355" s="2" t="n">
         <v>3.04</v>
       </c>
-      <c r="S355" t="n">
+      <c r="S355" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="T355" t="n">
+      <c r="T355" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="U355" t="n">
+      <c r="U355" s="2" t="n">
         <v>2.84</v>
       </c>
-      <c r="V355" t="n">
+      <c r="V355" s="2" t="n">
         <v>4.05</v>
       </c>
-      <c r="W355" t="n">
+      <c r="W355" s="2" t="n">
         <v>1.56</v>
       </c>
-      <c r="X355" t="n">
+      <c r="X355" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="Y355" t="n">
+      <c r="Y355" s="2" t="n">
         <v>7.65</v>
       </c>
-      <c r="Z355" t="n">
+      <c r="Z355" s="2" t="n">
         <v>0.97</v>
       </c>
-      <c r="AA355" t="n">
+      <c r="AA355" s="2" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026/5/29</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="C356" s="2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D356" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E356" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="F356" s="2" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="G356" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H356" s="2" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="I356" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="J356" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="K356" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="L356" s="2" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="M356" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N356" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O356" s="2" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="P356" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="Q356" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R356" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S356" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T356" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="U356" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="V356" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="W356" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X356" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y356" s="2" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="Z356" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AA356" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/01</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C357" s="2" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="D357" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E357" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="F357" s="2" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="G357" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H357" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I357" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="J357" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K357" s="2" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="L357" s="2" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="M357" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N357" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O357" s="2" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="P357" s="2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="Q357" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R357" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S357" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T357" s="2" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="U357" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V357" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="W357" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X357" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y357" s="2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="Z357" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AA357" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/02</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="C358" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="D358" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E358" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="F358" s="2" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="G358" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H358" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="I358" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="J358" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K358" s="2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="L358" s="2" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="M358" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N358" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O358" s="2" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="P358" s="2" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="Q358" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R358" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="S358" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T358" s="2" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="U358" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V358" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W358" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X358" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y358" s="2" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="Z358" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AA358" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/03</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="C359" s="2" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="D359" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E359" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="F359" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G359" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H359" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I359" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="J359" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K359" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="L359" s="2" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="M359" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N359" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O359" s="2" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="P359" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q359" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R359" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S359" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T359" s="2" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="U359" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V359" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W359" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X359" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y359" s="2" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="Z359" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AA359" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/04</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="C360" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="D360" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E360" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="F360" s="2" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="G360" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H360" s="2" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="I360" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="J360" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K360" s="2" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="L360" s="2" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="M360" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N360" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O360" s="2" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="P360" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="Q360" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R360" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S360" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T360" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="U360" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V360" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="W360" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X360" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y360" s="2" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="Z360" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA360" s="2" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/05</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C361" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D361" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E361" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="G361" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H361" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I361" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="J361" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="K361" s="2" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="L361" s="2" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="M361" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N361" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O361" s="2" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="P361" s="2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="Q361" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R361" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S361" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="T361" s="2" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="U361" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V361" s="2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W361" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X361" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y361" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z361" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA361" s="2" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/08</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C362" s="2" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="D362" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E362" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="F362" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="G362" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H362" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="I362" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J362" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K362" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L362" s="2" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="M362" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N362" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O362" s="2" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="P362" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q362" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R362" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S362" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T362" s="2" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="U362" s="2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V362" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="W362" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X362" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y362" s="2" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="Z362" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA362" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/09</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C363" s="2" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="D363" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E363" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="F363" s="2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="G363" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H363" s="2" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="I363" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J363" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="K363" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L363" s="2" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N363" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O363" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P363" s="2" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="Q363" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R363" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S363" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T363" s="2" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="U363" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V363" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="W363" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X363" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y363" s="2" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="Z363" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AA363" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/10</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C364" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="D364" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E364" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F364" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="G364" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H364" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I364" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="J364" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K364" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="L364" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N364" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O364" s="2" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="P364" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="Q364" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R364" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S364" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T364" s="2" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="U364" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V364" s="2" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="W364" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X364" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y364" s="2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="Z364" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AA364" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/11</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C365" s="2" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="D365" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E365" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="F365" s="2" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="G365" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H365" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I365" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="J365" s="2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="K365" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="L365" s="2" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N365" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O365" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="P365" s="2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q365" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R365" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S365" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T365" s="2" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="U365" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V365" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="W365" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X365" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y365" s="2" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="Z365" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AA365" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/12</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C366" s="2" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="D366" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E366" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="F366" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G366" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H366" s="2" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="I366" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="J366" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K366" s="2" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="L366" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M366" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N366" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O366" s="2" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="P366" s="2" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="Q366" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R366" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="S366" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T366" s="2" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="U366" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V366" s="2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="W366" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X366" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y366" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Z366" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AA366" s="2" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/15</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="C367" s="2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="D367" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E367" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F367" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G367" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H367" s="2" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I367" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="J367" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K367" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="L367" s="2" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="M367" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N367" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O367" s="2" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="P367" s="2" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="Q367" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R367" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S367" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T367" s="2" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="U367" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V367" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="W367" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X367" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y367" s="2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="Z367" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA367" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/16</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C368" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="D368" s="2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E368" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F368" s="2" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="G368" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H368" s="2" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="I368" s="2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="J368" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K368" s="2" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="L368" s="2" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="M368" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N368" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O368" s="2" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="P368" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="Q368" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R368" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S368" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T368" s="2" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="U368" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V368" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W368" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X368" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y368" s="2" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="Z368" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AA368" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/17</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="C369" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="D369" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E369" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="F369" s="2" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="G369" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H369" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="I369" s="2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="J369" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="K369" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="L369" s="2" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="M369" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N369" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O369" s="2" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="P369" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="Q369" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R369" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="S369" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T369" s="2" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="U369" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V369" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="W369" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X369" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y369" s="2" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="Z369" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AA369" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/18</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="C370" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="D370" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E370" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="F370" s="2" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="G370" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H370" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="I370" s="2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="J370" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="K370" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="L370" s="2" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="M370" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N370" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O370" s="2" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="P370" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="Q370" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R370" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="S370" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T370" s="2" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="U370" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V370" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="W370" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X370" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y370" s="2" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="Z370" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AA370" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/22</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C371" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="D371" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E371" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="F371" s="2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="G371" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H371" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="I371" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="J371" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="K371" s="2" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="L371" s="2" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="M371" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N371" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O371" s="2" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="P371" s="2" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="Q371" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R371" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="S371" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T371" s="2" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="U371" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V371" s="2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="W371" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X371" s="2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y371" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z371" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AA371" s="2" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/23</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="C372" s="2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="D372" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E372" s="2" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="F372" s="2" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="G372" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H372" s="2" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="I372" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J372" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="K372" s="2" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="L372" s="2" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="M372" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N372" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O372" s="2" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="P372" s="2" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="Q372" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R372" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="S372" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T372" s="2" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="U372" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V372" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="W372" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X372" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y372" s="2" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Z372" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AA372" s="2" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/24</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="C373" s="2" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="D373" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E373" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F373" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G373" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H373" s="2" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="I373" s="2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J373" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="K373" s="2" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="L373" s="2" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="M373" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N373" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O373" s="2" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="P373" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q373" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R373" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S373" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T373" s="2" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="U373" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V373" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="W373" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X373" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y373" s="2" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="Z373" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AA373" s="2" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/25</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C374" s="2" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="D374" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E374" s="2" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="F374" s="2" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="G374" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H374" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="I374" s="2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="J374" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="K374" s="2" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="L374" s="2" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="M374" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N374" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O374" s="2" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="P374" s="2" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="Q374" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R374" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S374" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T374" s="2" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="U374" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="V374" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="W374" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X374" s="2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y374" s="2" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="Z374" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AA374" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/26</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="C375" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="D375" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="E375" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="F375" s="2" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="G375" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H375" s="2" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="I375" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="J375" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="K375" s="2" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="L375" s="2" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="M375" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N375" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O375" s="2" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="P375" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="Q375" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R375" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S375" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T375" s="2" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="U375" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="V375" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="W375" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X375" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y375" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z375" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AA375" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026/6/29</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="C376" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="D376" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E376" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F376" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="G376" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H376" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I376" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="J376" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K376" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="L376" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="M376" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N376" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O376" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="P376" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R376" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S376" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T376" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="U376" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V376" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="W376" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X376" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y376" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="Z376" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AA376" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>
